--- a/Paket_7_Matematika_TKA_SD.xlsx
+++ b/Paket_7_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 7 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Sebuah pabrik roti memproduksi 120 kotak biskuit setiap hari. Setiap kotak berisi 24 bungkus biskuit. Seluruh biskuit dari hasil produksi 3 hari akan dikirimkan kepada 18 toko langganan sama banyak. Berapa bungkus biskuit yang diterima setiap toko?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 360 bungkus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 480 bungkus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 540 bungkus</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 600 bungkus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Suhu awal air di dalam wadah adalah 28°C. Wadah dimasukkan ke dalam ruang pendingin sehingga suhunya turun 4°C setiap 12 menit. Berapakah suhu air tersebut setelah berada di dalam ruang pendingin selama 1,5 jam (90 menit)?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. -4°C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. -2°C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 0°C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 2°C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Seorang penjahit memiliki persediaan kain sepanjang 15,5 meter. Sebanyak 6 1/4 meter digunakan untuk membuat kemeja pria dan 4,75 meter untuk membuat gamis anak. Berapa meter sisa kain penjahit tersebut?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 4,25 meter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4,50 meter</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 4,75 meter</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 5,00 meter</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Lampu mercusuar merah berkedip setiap 12 detik, lampu hijau setiap 15 detik, dan lampu kuning setiap 20 detik. Jika ketiga lampu berkedip bersamaan pertama kali pada pukul 20.00.00, pada pukul berapa ketiga lampu akan berkedip bersamaan untuk ketiga kalinya?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 20.01.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 20.02.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 20.03.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 20.04.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,17 +637,21 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Ibu Marni membuat 60 kue pastel, 75 lemper ayam, dan 90 risoles mayo untuk disajikan ke dalam piring-piring hidangan arisan. Setiap piring berisi ketiga jenis kue dengan jumlah yang sama banyak. Manakah pernyataan yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Jumlah piring hidangan terbanyak yang harus disiapkan Ibu Marni adalah 15 piring ☐ B. Setiap piring berisi 4 kue pastel dan 5 lemper ayam ☐ C. Setiap piring berisi 7 risoles mayo ☐ D. Total seluruh kue yang ada di dalam masing-masing piring adalah 15 buah kue [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -666,7 +682,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +696,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Jarak antara Kota Melati dan Kota Mawar pada peta adalah 7,5 cm. Jika skala peta yang digunakan adalah 1 : 1.200.000, berapakah jarak sebenarnya antara kedua kota tersebut?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 80 km</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 90 km</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 100 km</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 110 km</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +727,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Pak Surya membagikan hasil panen madu hutan sebanyak 24 liter kepada tiga kelompok tani binaannya: • Kelompok Tani Barokah menerima 3/8 bagian • Kelompok Tani Makmur menerima 1/3 bagian • Kelompok Tani Sejahtera menerima sisanya Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +772,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +786,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Jalan desa sepanjang 3,2 km diaspal dalam tiga tahap. Tahap pertama diselesaikan sepanjang 1.450 meter dan tahap kedua sepanjang 95 dam. Berapa meterkah panjang jalan yang harus diaspal pada tahap ketiga?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 700 meter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 750 meter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 800 meter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 850 meter</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +817,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +831,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Jarak kota P dan kota Q adalah 150 km. Dari kota P, mobil A melaju menuju kota Q pada pukul 08.00 dengan kecepatan rata-rata 40 km/jam. Pada saat yang sama, dari kota Q mobil B melaju menuju kota P melalui jalan yang sama dengan kecepatan rata-rata 60 km/jam. Pada pukul berapakah kedua mobil tersebut akan berpapasan di jalan?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 09.00 WIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 09.30 WIB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 09.45 WIB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 10.00 WIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +862,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +876,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Kakek memiliki tanah seluas 1,2 hektare. Di atas tanah tersebut dibangun rumah seluas 650 m², kolam ikan seluas 15 are, dan sisanya ditanami pohon jati. Berapakah luas tanah yang ditanami pohon jati?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 9.850 m²</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 10.150 m²</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 10.350 m²</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 10.850 m²</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +907,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +921,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Kran air dapat mengalirkan air sebanyak 180 liter dalam waktu 15 menit. Jika sebuah kolam penampungan bervolume 1,44 m³ hendak diisi penuh menggunakan kran tersebut, berapa jam waktu yang diperlukan?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1,5 jam</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 2 jam</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2,5 jam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 3 jam</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,17 +952,21 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan bangun datar belah ketupat ABCD dengan panjang sisi 10 cm serta panjang diagonal AC = 16 cm dan BD = 12 cm. Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Keliling belah ketupat ABCD adalah 40 cm ☐ B. Luas belah ketupat ABCD adalah 96 cm² ☐ C. Kedua diagonal belah ketupat saling berpotongan tegak lurus dan saling membagi dua sama panjang ☐ D. Belah ketupat memiliki 4 sumbu simetri lipat [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -953,7 +997,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Pak Johan membuat papan nama kantor berbentuk gabungan persegi panjang berukuran 40 cm × 25 cm dan segitiga sama kaki di atasnya dengan alas 40 cm dan tinggi 15 cm. Berapakah luas total papan nama tersebut?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.150 cm²</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1.200 cm²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 1.300 cm²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 1.450 cm²</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1042,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1056,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah wadah berbentuk prisma tegak segitiga siku-siku memiliki panjang sisi siku-siku alas 12 cm dan 16 cm. Jika tinggi prisma tersebut adalah 30 cm, berapakah volume prisma tersebut?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 2.400 cm³</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 2.880 cm³</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 3.240 cm³</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 5.760 cm³</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1087,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kotak kardus berbentuk balok berukuran panjang 40 cm, lebar 30 cm, dan tinggi 20 cm. Seluruh permukaan luar kotak akan dilapisi lakban bening. Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1132,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1146,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Nilai rata-rata ulangan harian matematika dari 19 siswa adalah 76. Jika nilai Fathan yang baru mengikuti ulangan susulan digabungkan, nilai rata-rata seluruh siswa naik menjadi 77. Berapakah nilai ulangan yang diperoleh Fathan?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 86</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 92</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 96</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1177,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1191,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Berikut adalah tabel data berat badan siswa kelas VI SD Merdeka: Berat (kg): 34 (4 siswa), 35 (6 siswa), 36 (8 siswa), 37 (5 siswa), 38 (2 siswa). Modus dan median dari berat badan siswa tersebut berturut-turut adalah...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Modus = 36 kg dan Median = 35,5 kg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Modus = 36 kg dan Median = 36 kg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Modus = 8 siswa dan Median = 36 kg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Modus = 36 kg dan Median = 36,5 kg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,17 +1222,21 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Catatan suhu tubuh seorang pasien di rumah sakit dari pukul 06.00 hingga 18.00 terdata sebagai berikut: • Pukul 06.00: 38,5°C • Pukul 09.00: 38,0°C • Pukul 12.00: 37,2°C • Pukul 15.00: 36,8°C • Pukul 18.00: 36,5°C Manakah pernyataan berikut yang BENAR terkait data suhu tersebut? (Jawaban benar lebih dari satu) ☐ A. Suhu tubuh pasien mengalami tren penurunan yang konsisten sepanjang hari ☐ B. Penurunan suhu tubuh paling signifikan terjadi antara pukul 09.00 hingga 12.00 sebesar 0,8°C ☐ C. Suhu tubuh pasien tertinggi tercatat pada pukul 18.00 ☐ D. Total penurunan suhu tubuh pasien dari pukul 06.00 hingga 18.00 adalah 2,0°C [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1199,7 +1267,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1281,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Titik P(4, -3) dicerminkan terhadap sumbu horizontal X. Koordinat bayangan titik P' hasil pencerminan tersebut adalah...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. P'(-4, -3)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. P'(4, 3)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. P'(-4, 3)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. P'(3, 4)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1312,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 7] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Pedagang buah membeli 1 peti mangga seharga Rp360.000 dengan berat kotor (bruto) 32 kg dan berat peti kayu (tara) 2 kg. Pedagang kemudian menjual seluruh daging buah mangga dengan harga Rp15.000 per kilogram. Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1357,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
